--- a/rules/CORE-000066/negative/01/data/unit-test-coreid-CG0639-negative.xlsx
+++ b/rules/CORE-000066/negative/01/data/unit-test-coreid-CG0639-negative.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\CORE-000066\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004422E2-E871-4842-A6A5-D9E51E3072E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4DB569-5D2F-48B5-BB33-BFC7A5108BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21240" windowHeight="15270" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="210">
   <si>
     <t>Product</t>
   </si>
@@ -294,72 +294,6 @@
     <t>1999-06-19</t>
   </si>
   <si>
-    <t>WBC</t>
-  </si>
-  <si>
-    <t>Leukocytes</t>
-  </si>
-  <si>
-    <t>HEMATOLOGY</t>
-  </si>
-  <si>
-    <t>10^9/L</t>
-  </si>
-  <si>
-    <t>NUMBER CONCENTRATION</t>
-  </si>
-  <si>
-    <t>6690-2</t>
-  </si>
-  <si>
-    <t>BLOOD</t>
-  </si>
-  <si>
-    <t>AUTOMATED COUNT</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>pH</t>
-  </si>
-  <si>
-    <t>URINALYSIS</t>
-  </si>
-  <si>
-    <t>LOG SUBSTANCE CONCENTRATION</t>
-  </si>
-  <si>
-    <t>5803-2</t>
-  </si>
-  <si>
-    <t>URINE</t>
-  </si>
-  <si>
-    <t>TEST STRIP</t>
-  </si>
-  <si>
-    <t>CHOL</t>
-  </si>
-  <si>
-    <t>Cholesterol</t>
-  </si>
-  <si>
-    <t>mg/dL</t>
-  </si>
-  <si>
-    <t>&lt;200</t>
-  </si>
-  <si>
-    <t>2093-3</t>
-  </si>
-  <si>
-    <t>Week 2</t>
-  </si>
-  <si>
-    <t>1999-07-21</t>
-  </si>
-  <si>
     <t>Laboratory Results</t>
   </si>
   <si>
@@ -627,42 +561,6 @@
     <t>2013-05-20</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>FATIGUE</t>
-  </si>
-  <si>
-    <t>DOSE NOT CHANGED</t>
-  </si>
-  <si>
-    <t>UNLIKELY RELATED</t>
-  </si>
-  <si>
-    <t>2013-01-14</t>
-  </si>
-  <si>
-    <t>CDISC002</t>
-  </si>
-  <si>
-    <t>MILD</t>
-  </si>
-  <si>
-    <t>POSSIBLY RELATED</t>
-  </si>
-  <si>
-    <t>2012-11-16</t>
-  </si>
-  <si>
-    <t>SHOULDER PAIN</t>
-  </si>
-  <si>
-    <t>NOT RELATED</t>
-  </si>
-  <si>
-    <t>2012-11-21</t>
-  </si>
-  <si>
     <t>CMSEQ</t>
   </si>
   <si>
@@ -757,27 +655,6 @@
   </si>
   <si>
     <t>2013-04-29</t>
-  </si>
-  <si>
-    <t>METAMUCIL</t>
-  </si>
-  <si>
-    <t>PRN</t>
-  </si>
-  <si>
-    <t>2012-08</t>
-  </si>
-  <si>
-    <t>HYDROCORTISONE, TOPICAL</t>
-  </si>
-  <si>
-    <t>BID</t>
-  </si>
-  <si>
-    <t>TOPICAL</t>
-  </si>
-  <si>
-    <t>2013-01-11</t>
   </si>
 </sst>
 </file>
@@ -816,7 +693,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -833,12 +710,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
   </fills>
@@ -884,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -893,12 +764,9 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -906,9 +774,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1340,23 +1205,23 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1402,11 +1267,11 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1414,7 +1279,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -1422,11 +1287,11 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>115</v>
+      <c r="E3" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1434,7 +1299,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -1442,11 +1307,11 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>116</v>
+      <c r="E4" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1456,10 +1321,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AV8"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:48" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -1550,663 +1415,360 @@
       <c r="AD1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
     </row>
-    <row r="2" spans="1:48" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:30" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="V2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="Z2" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AA2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AB2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AC2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AD2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-      <c r="AK2" s="6"/>
-      <c r="AL2" s="6"/>
-      <c r="AM2" s="6"/>
-      <c r="AN2" s="6"/>
-      <c r="AO2" s="6"/>
-      <c r="AP2" s="6"/>
-      <c r="AQ2" s="6"/>
-      <c r="AR2" s="6"/>
-      <c r="AS2" s="6"/>
-      <c r="AT2" s="6"/>
-      <c r="AU2" s="6"/>
-      <c r="AV2" s="6"/>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="5" t="s">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="E3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q3" s="5" t="s">
+      <c r="P3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z3" s="5" t="s">
+      <c r="S3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AA3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC3" s="5" t="s">
+      <c r="AA3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AD3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="7"/>
-      <c r="AI3" s="7"/>
-      <c r="AJ3" s="7"/>
-      <c r="AK3" s="7"/>
-      <c r="AL3" s="7"/>
-      <c r="AM3" s="7"/>
-      <c r="AN3" s="7"/>
-      <c r="AO3" s="7"/>
-      <c r="AP3" s="7"/>
-      <c r="AQ3" s="7"/>
-      <c r="AR3" s="7"/>
-      <c r="AS3" s="7"/>
-      <c r="AT3" s="7"/>
-      <c r="AU3" s="7"/>
-      <c r="AV3" s="7"/>
+      <c r="AD3" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>50</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>50</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>50</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>50</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>50</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>50</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>50</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>50</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>50</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>50</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>50</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>50</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="4">
         <v>50</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="4">
         <v>8</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="4">
         <v>50</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="4">
         <v>8</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="4">
         <v>8</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="4">
         <v>50</v>
       </c>
-      <c r="T4" s="5">
+      <c r="T4" s="4">
         <v>50</v>
       </c>
-      <c r="U4" s="5">
+      <c r="U4" s="4">
         <v>50</v>
       </c>
-      <c r="V4" s="5">
+      <c r="V4" s="4">
         <v>50</v>
       </c>
-      <c r="W4" s="5">
+      <c r="W4" s="4">
         <v>50</v>
       </c>
-      <c r="X4" s="5">
+      <c r="X4" s="4">
         <v>50</v>
       </c>
-      <c r="Y4" s="5">
+      <c r="Y4" s="4">
         <v>50</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4" s="4">
         <v>8</v>
       </c>
-      <c r="AA4" s="5">
+      <c r="AA4" s="4">
         <v>50</v>
       </c>
-      <c r="AB4" s="5">
+      <c r="AB4" s="4">
         <v>50</v>
       </c>
-      <c r="AC4" s="5">
+      <c r="AC4" s="4">
         <v>8</v>
       </c>
-      <c r="AD4" s="5">
+      <c r="AD4" s="4">
         <v>50</v>
       </c>
-      <c r="AE4" s="7"/>
-      <c r="AF4" s="7"/>
-      <c r="AG4" s="7"/>
-      <c r="AH4" s="7"/>
-      <c r="AI4" s="7"/>
-      <c r="AJ4" s="7"/>
-      <c r="AK4" s="7"/>
-      <c r="AL4" s="7"/>
-      <c r="AM4" s="7"/>
-      <c r="AN4" s="7"/>
-      <c r="AO4" s="7"/>
-      <c r="AP4" s="7"/>
-      <c r="AQ4" s="7"/>
-      <c r="AR4" s="7"/>
-      <c r="AS4" s="7"/>
-      <c r="AT4" s="7"/>
-      <c r="AU4" s="7"/>
-      <c r="AV4" s="7"/>
     </row>
-    <row r="5" spans="1:48" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="8">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="5">
         <v>2.5</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="5">
         <v>0.5</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="5">
         <v>10</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="5">
         <v>2.5</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="5">
         <v>2.5</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="5">
         <v>0.5</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="5">
         <v>10</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="U5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="V5" s="8" t="s">
+      <c r="V5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="X5" s="8" t="s">
+      <c r="X5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Y5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="Z5" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="8" t="s">
+      <c r="Z5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="AB5" s="8" t="s">
+      <c r="AB5" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="AD5" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:48" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="8">
-        <v>2</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="8">
-        <v>5.9</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="L6" s="8">
-        <v>4</v>
-      </c>
-      <c r="M6" s="8">
-        <v>11</v>
-      </c>
-      <c r="N6" s="8">
-        <v>5.9</v>
-      </c>
-      <c r="O6" s="8">
-        <v>5.9</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>4</v>
-      </c>
-      <c r="R6" s="8">
-        <v>11</v>
-      </c>
-      <c r="U6" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="V6" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="W6" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="X6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z6" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB6" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD6" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:48" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="8">
-        <v>3</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="8">
-        <v>7.5</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="L7" s="8">
-        <v>5</v>
-      </c>
-      <c r="M7" s="8">
-        <v>9</v>
-      </c>
-      <c r="N7" s="8">
-        <v>7.5</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>5</v>
-      </c>
-      <c r="R7" s="8">
-        <v>9</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="W7" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y7" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z7" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB7" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD7" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:48" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="8">
-        <v>4</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="8">
-        <v>229</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="L8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="N8" s="8">
-        <v>229</v>
-      </c>
-      <c r="O8" s="8">
-        <v>229</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
-        <v>199</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z8" s="8">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB8" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD8" s="8" t="s">
+      <c r="AD5" s="5" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2217,815 +1779,557 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7804E873-A290-41D5-AF31-FC6A63443110}">
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:38" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA1" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="AB1" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="AC1" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H1" s="10" t="s">
+      <c r="AD1" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="AE1" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="AF1" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="AG1" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="AH1" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="AI1" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="AK1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="AL1" s="7" t="s">
         <v>130</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="S1" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="V1" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="Z1" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA1" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB1" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD1" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="AE1" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="AG1" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="AH1" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI1" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ1" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="AK1" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="AL1" s="10" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:38" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB2" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="AC2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="11" t="s">
+      <c r="AD2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="AE2" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="AF2" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="AG2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="AH2" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="AI2" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="AK2" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="AL2" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG2" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI2" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="AJ2" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="AK2" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="AL2" s="11" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="A3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="E3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="T3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="U3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="V3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="X3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI3" s="12" t="s">
+      <c r="H3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AJ3" s="12" t="s">
+      <c r="AJ3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AK3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AL3" s="12" t="s">
+      <c r="AK3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL3" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+      <c r="A4" s="4">
         <v>12</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="4">
         <v>8</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="4">
         <v>8</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="4">
         <v>50</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="4">
         <v>200</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>8</v>
       </c>
-      <c r="H4" s="11">
-        <v>1</v>
-      </c>
-      <c r="I4" s="11">
-        <v>1</v>
-      </c>
-      <c r="J4" s="11">
-        <v>1</v>
-      </c>
-      <c r="K4" s="11">
-        <v>1</v>
-      </c>
-      <c r="L4" s="11">
-        <v>1</v>
-      </c>
-      <c r="M4" s="11">
-        <v>1</v>
-      </c>
-      <c r="N4" s="11">
-        <v>1</v>
-      </c>
-      <c r="O4" s="11">
-        <v>1</v>
-      </c>
-      <c r="P4" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>1</v>
-      </c>
-      <c r="R4" s="11">
-        <v>1</v>
-      </c>
-      <c r="S4" s="11">
-        <v>1</v>
-      </c>
-      <c r="T4" s="11">
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1</v>
+      </c>
+      <c r="R4" s="4">
+        <v>1</v>
+      </c>
+      <c r="S4" s="4">
+        <v>1</v>
+      </c>
+      <c r="T4" s="4">
         <v>8</v>
       </c>
-      <c r="U4" s="11">
-        <v>1</v>
-      </c>
-      <c r="V4" s="11">
+      <c r="U4" s="4">
+        <v>1</v>
+      </c>
+      <c r="V4" s="4">
         <v>16</v>
       </c>
-      <c r="W4" s="11">
+      <c r="W4" s="4">
         <v>16</v>
       </c>
-      <c r="X4" s="11">
+      <c r="X4" s="4">
         <v>32</v>
       </c>
-      <c r="Y4" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="11">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="11">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="11">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="11">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="11">
+      <c r="Y4" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="4">
         <v>9</v>
       </c>
-      <c r="AG4" s="11">
+      <c r="AG4" s="4">
         <v>10</v>
       </c>
-      <c r="AH4" s="11">
+      <c r="AH4" s="4">
         <v>10</v>
       </c>
-      <c r="AI4" s="11">
+      <c r="AI4" s="4">
         <v>8</v>
       </c>
-      <c r="AJ4" s="11">
+      <c r="AJ4" s="4">
         <v>8</v>
       </c>
-      <c r="AK4" s="11">
+      <c r="AK4" s="4">
         <v>7</v>
       </c>
-      <c r="AL4" s="11">
+      <c r="AL4" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="12">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="U5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="V5" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="W5" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="X5" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AC5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AD5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AE5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AF5" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG5" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="12">
+      <c r="A5" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="AC5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="AD5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="AF5" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="AG5" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="AH5" s="8"/>
+      <c r="AI5" s="8">
         <v>3</v>
       </c>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="AL5" s="12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="11">
-        <v>2</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="U6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="V6" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="W6" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="X6" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AC6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AD6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AE6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AF6" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG6" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="11">
-        <v>46</v>
-      </c>
-      <c r="AJ6" s="11"/>
-      <c r="AK6" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="AL6" s="11" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:38" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="12">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y7" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z7" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA7" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB7" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AC7" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AD7" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AE7" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AF7" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG7" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12">
-        <v>2</v>
-      </c>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="AL7" s="12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D8" s="11">
-        <v>2</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="U8" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="V8" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="W8" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="X8" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y8" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z8" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA8" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB8" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AC8" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AD8" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AE8" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="AF8" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG8" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="11">
-        <v>7</v>
-      </c>
-      <c r="AJ8" s="11"/>
-      <c r="AK8" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="AL8" s="11" t="s">
-        <v>204</v>
+      <c r="AJ5" s="8"/>
+      <c r="AK5" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL5" s="8" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3040,388 +2344,285 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A21FB8-E6EF-4361-A0DF-58A3A47124EB}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>146</v>
+      <c r="D1" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>224</v>
+        <v>94</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="E2" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>185</v>
+      <c r="M2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="A3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="12" t="s">
+      <c r="E3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="H3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="M3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="O3" s="12" t="s">
+      <c r="M3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="Q3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="12" t="s">
+      <c r="Q3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="R3" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+      <c r="A4" s="4">
         <v>12</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="4">
         <v>8</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="4">
         <v>8</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="4">
         <v>200</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="4">
         <v>200</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="4">
         <v>8</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="4">
         <v>6</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="4">
         <v>3</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="4">
         <v>24</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="4">
         <v>9</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>8</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="4">
         <v>10</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="4">
         <v>10</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="4">
         <v>8</v>
       </c>
-      <c r="P4" s="11">
+      <c r="P4" s="4">
         <v>8</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="4">
         <v>7</v>
       </c>
-      <c r="R4" s="11">
+      <c r="R4" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="12">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="G5" s="12">
-        <v>1</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12">
+      <c r="A5" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8">
         <v>151</v>
       </c>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-    </row>
-    <row r="6" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="11">
-        <v>2</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="G6" s="11">
-        <v>1</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="R6" s="11" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="12">
-        <v>3</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="G7" s="12">
-        <v>1</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12">
-        <v>43</v>
-      </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>199</v>
-      </c>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:R4 A2:K2 M2:R2">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="2">
+  <conditionalFormatting sqref="A2:R4">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A2))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(L2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
